--- a/Input/Config.xlsx
+++ b/Input/Config.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Input/Config.xlsx
+++ b/Input/Config.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
